--- a/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
+++ b/ssp_modeling/cost-benefits/cb_config_files/cb_config_params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_libya/ssp_modeling/cost-benefits/cb_config_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fabianfuentes/git/ssp_morocco/ssp_modeling/cost-benefits/cb_config_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D9FB434-3019-0A41-8122-C89FDCF717AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE71E4E-0326-F648-BF3F-99F95D890A54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51200" yWindow="600" windowWidth="51200" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-51200" yWindow="600" windowWidth="51200" windowHeight="28200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tx_table" sheetId="1" r:id="rId1"/>
@@ -24115,7 +24115,7 @@
         <v>590</v>
       </c>
       <c r="I26" s="2">
-        <v>-400</v>
+        <v>-4000</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>587</v>
